--- a/data/derived_data/4_Diversities/ps_ITS_rare_expe_D1_20_otu_table.xlsx
+++ b/data/derived_data/4_Diversities/ps_ITS_rare_expe_D1_20_otu_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="331">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -905,9 +905,6 @@
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_729</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
@@ -1913,7 +1910,7 @@
         <v>2125</v>
       </c>
       <c r="BL2" t="n">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="BM2" t="n">
         <v>2075</v>
@@ -2772,7 +2769,7 @@
         <v>84</v>
       </c>
       <c r="CO4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CP4" t="n">
         <v>56</v>
@@ -8948,7 +8945,7 @@
         <v>114</v>
       </c>
       <c r="CO20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="CP20" t="n">
         <v>0</v>
@@ -9471,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
         <v>17</v>
@@ -10791,7 +10788,7 @@
         <v>0</v>
       </c>
       <c r="BL25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BM25" t="n">
         <v>4</v>
@@ -14352,7 +14349,7 @@
         <v>4</v>
       </c>
       <c r="CO34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CP34" t="n">
         <v>0</v>
@@ -15731,7 +15728,7 @@
         <v>17</v>
       </c>
       <c r="AL38" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
@@ -17440,7 +17437,7 @@
         <v>123</v>
       </c>
       <c r="CO42" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="CP42" t="n">
         <v>190</v>
@@ -19669,7 +19666,7 @@
         <v>20</v>
       </c>
       <c r="BL48" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="BM48" t="n">
         <v>430</v>
@@ -19750,7 +19747,7 @@
         <v>37</v>
       </c>
       <c r="CM48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CN48" t="n">
         <v>0</v>
@@ -19893,10 +19890,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -26237,7 +26234,7 @@
         <v>0</v>
       </c>
       <c r="BN65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BO65" t="n">
         <v>0</v>
@@ -26841,7 +26838,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
         <v>2</v>
@@ -27230,7 +27227,7 @@
         <v>26</v>
       </c>
       <c r="K68" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -28855,7 +28852,7 @@
         <v>0</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM72" t="n">
         <v>0</v>
@@ -29319,7 +29316,7 @@
         <v>0</v>
       </c>
       <c r="BL73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BM73" t="n">
         <v>0</v>
@@ -30315,7 +30312,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K76" t="n">
         <v>7</v>
@@ -32030,7 +32027,7 @@
         <v>105</v>
       </c>
       <c r="BO80" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BP80" t="n">
         <v>0</v>
@@ -33403,7 +33400,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -33789,7 +33786,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K85" t="n">
         <v>7</v>
@@ -34175,7 +34172,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K86" t="n">
         <v>5</v>
@@ -36108,7 +36105,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -36267,7 +36264,7 @@
         <v>16</v>
       </c>
       <c r="BL91" t="n">
-        <v>3228</v>
+        <v>3230</v>
       </c>
       <c r="BM91" t="n">
         <v>2348</v>
@@ -37266,7 +37263,7 @@
         <v>5</v>
       </c>
       <c r="K94" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -39056,7 +39053,7 @@
         <v>109</v>
       </c>
       <c r="CO98" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="CP98" t="n">
         <v>224</v>
@@ -41877,7 +41874,7 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -44986,7 +44983,7 @@
         <v>37</v>
       </c>
       <c r="K114" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -47847,7 +47844,7 @@
         <v>0</v>
       </c>
       <c r="BL121" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BM121" t="n">
         <v>10</v>
@@ -49391,7 +49388,7 @@
         <v>0</v>
       </c>
       <c r="BL125" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BM125" t="n">
         <v>0</v>
@@ -53251,7 +53248,7 @@
         <v>0</v>
       </c>
       <c r="BL135" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BM135" t="n">
         <v>17</v>
@@ -54023,7 +54020,7 @@
         <v>0</v>
       </c>
       <c r="BL137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BM137" t="n">
         <v>1</v>
@@ -54882,7 +54879,7 @@
         <v>114</v>
       </c>
       <c r="CO139" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="CP139" t="n">
         <v>217</v>
@@ -59651,10 +59648,10 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K152" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -62524,7 +62521,7 @@
         <v>0</v>
       </c>
       <c r="BO159" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BP159" t="n">
         <v>0</v>
@@ -63374,7 +63371,7 @@
         <v>0</v>
       </c>
       <c r="CO161" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CP161" t="n">
         <v>0</v>
@@ -64831,7 +64828,7 @@
         <v>0</v>
       </c>
       <c r="BL165" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BM165" t="n">
         <v>13</v>
@@ -65989,7 +65986,7 @@
         <v>0</v>
       </c>
       <c r="BL168" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BM168" t="n">
         <v>16</v>
@@ -66961,10 +66958,10 @@
         <v>297</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -66994,7 +66991,7 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="N171" t="n">
         <v>0</v>
@@ -67036,10 +67033,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -67066,10 +67063,10 @@
         <v>0</v>
       </c>
       <c r="AK171" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AL171" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AM171" t="n">
         <v>0</v>
@@ -67096,10 +67093,10 @@
         <v>0</v>
       </c>
       <c r="AU171" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AV171" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AW171" t="n">
         <v>0</v>
@@ -67126,10 +67123,10 @@
         <v>0</v>
       </c>
       <c r="BE171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF171" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG171" t="n">
         <v>0</v>
@@ -67147,16 +67144,16 @@
         <v>0</v>
       </c>
       <c r="BL171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM171" t="n">
         <v>0</v>
       </c>
       <c r="BN171" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BO171" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BP171" t="n">
         <v>0</v>
@@ -67165,7 +67162,7 @@
         <v>0</v>
       </c>
       <c r="BR171" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="BS171" t="n">
         <v>0</v>
@@ -67195,10 +67192,10 @@
         <v>0</v>
       </c>
       <c r="CB171" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CC171" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CD171" t="n">
         <v>0</v>
@@ -67213,7 +67210,7 @@
         <v>0</v>
       </c>
       <c r="CH171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI171" t="n">
         <v>0</v>
@@ -67228,22 +67225,22 @@
         <v>0</v>
       </c>
       <c r="CM171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN171" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CO171" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CP171" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="CQ171" t="n">
         <v>0</v>
       </c>
       <c r="CR171" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="CS171" t="n">
         <v>0</v>
@@ -67273,13 +67270,13 @@
         <v>0</v>
       </c>
       <c r="DB171" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="DC171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="DD171" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DE171" t="n">
         <v>0</v>
@@ -67318,7 +67315,7 @@
         <v>0</v>
       </c>
       <c r="DQ171" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DR171" t="n">
         <v>0</v>
@@ -67339,7 +67336,7 @@
         <v>0</v>
       </c>
       <c r="DX171" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172">
@@ -67347,10 +67344,10 @@
         <v>298</v>
       </c>
       <c r="B172" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -67380,7 +67377,7 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
         <v>0</v>
@@ -67422,10 +67419,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -67446,16 +67443,16 @@
         <v>0</v>
       </c>
       <c r="AI172" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ172" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK172" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AL172" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="AM172" t="n">
         <v>0</v>
@@ -67482,10 +67479,10 @@
         <v>0</v>
       </c>
       <c r="AU172" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AV172" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AW172" t="n">
         <v>0</v>
@@ -67512,10 +67509,10 @@
         <v>0</v>
       </c>
       <c r="BE172" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BF172" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG172" t="n">
         <v>0</v>
@@ -67539,10 +67536,10 @@
         <v>0</v>
       </c>
       <c r="BN172" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BO172" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BP172" t="n">
         <v>0</v>
@@ -67551,7 +67548,7 @@
         <v>0</v>
       </c>
       <c r="BR172" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="BS172" t="n">
         <v>0</v>
@@ -67581,10 +67578,10 @@
         <v>0</v>
       </c>
       <c r="CB172" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CC172" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CD172" t="n">
         <v>0</v>
@@ -67599,7 +67596,7 @@
         <v>0</v>
       </c>
       <c r="CH172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CI172" t="n">
         <v>0</v>
@@ -67617,19 +67614,19 @@
         <v>0</v>
       </c>
       <c r="CN172" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CO172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CP172" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="CQ172" t="n">
         <v>0</v>
       </c>
       <c r="CR172" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="CS172" t="n">
         <v>0</v>
@@ -67659,13 +67656,13 @@
         <v>0</v>
       </c>
       <c r="DB172" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="DC172" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="DD172" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DE172" t="n">
         <v>0</v>
@@ -67704,7 +67701,7 @@
         <v>0</v>
       </c>
       <c r="DQ172" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DR172" t="n">
         <v>0</v>
@@ -67725,7 +67722,7 @@
         <v>0</v>
       </c>
       <c r="DX172" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -67739,13 +67736,13 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -67832,10 +67829,10 @@
         <v>0</v>
       </c>
       <c r="AI173" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ173" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AK173" t="n">
         <v>0</v>
@@ -68125,13 +68122,13 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -68194,10 +68191,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -68311,7 +68308,7 @@
         <v>0</v>
       </c>
       <c r="BN174" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO174" t="n">
         <v>0</v>
@@ -68505,10 +68502,10 @@
         <v>301</v>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -68580,10 +68577,10 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
         <v>0</v>
@@ -68673,7 +68670,7 @@
         <v>0</v>
       </c>
       <c r="BF175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG175" t="n">
         <v>0</v>
@@ -68697,7 +68694,7 @@
         <v>0</v>
       </c>
       <c r="BN175" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO175" t="n">
         <v>0</v>
@@ -68739,7 +68736,7 @@
         <v>0</v>
       </c>
       <c r="CB175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CC175" t="n">
         <v>0</v>
@@ -68891,10 +68888,10 @@
         <v>302</v>
       </c>
       <c r="B176" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -69059,7 +69056,7 @@
         <v>0</v>
       </c>
       <c r="BF176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG176" t="n">
         <v>0</v>
@@ -69098,7 +69095,7 @@
         <v>0</v>
       </c>
       <c r="BS176" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BT176" t="n">
         <v>0</v>
@@ -69125,7 +69122,7 @@
         <v>0</v>
       </c>
       <c r="CB176" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CC176" t="n">
         <v>0</v>
@@ -69137,7 +69134,7 @@
         <v>0</v>
       </c>
       <c r="CF176" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CG176" t="n">
         <v>0</v>
@@ -69277,7 +69274,7 @@
         <v>303</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -69292,7 +69289,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -69484,7 +69481,7 @@
         <v>0</v>
       </c>
       <c r="BS177" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BT177" t="n">
         <v>0</v>
@@ -69523,7 +69520,7 @@
         <v>0</v>
       </c>
       <c r="CF177" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CG177" t="n">
         <v>0</v>
@@ -69663,7 +69660,7 @@
         <v>304</v>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -69678,266 +69675,266 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0</v>
+      </c>
+      <c r="V178" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>226</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>98</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>44</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>3</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI178" t="n">
+        <v>57</v>
+      </c>
+      <c r="CJ178" t="n">
+        <v>14</v>
+      </c>
+      <c r="CK178" t="n">
+        <v>19</v>
+      </c>
+      <c r="CL178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO178" t="n">
         <v>6</v>
       </c>
-      <c r="H178" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178" t="n">
-        <v>0</v>
-      </c>
-      <c r="J178" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" t="n">
-        <v>0</v>
-      </c>
-      <c r="N178" t="n">
-        <v>0</v>
-      </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="n">
-        <v>0</v>
-      </c>
-      <c r="T178" t="n">
-        <v>0</v>
-      </c>
-      <c r="U178" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" t="n">
-        <v>0</v>
-      </c>
-      <c r="W178" t="n">
-        <v>0</v>
-      </c>
-      <c r="X178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY178" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN178" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO178" t="n">
-        <v>0</v>
-      </c>
       <c r="CP178" t="n">
         <v>0</v>
       </c>
@@ -69957,7 +69954,7 @@
         <v>0</v>
       </c>
       <c r="CV178" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="CW178" t="n">
         <v>0</v>
@@ -69978,7 +69975,7 @@
         <v>0</v>
       </c>
       <c r="DC178" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DD178" t="n">
         <v>0</v>
@@ -70002,10 +69999,10 @@
         <v>0</v>
       </c>
       <c r="DK178" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DL178" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="DM178" t="n">
         <v>0</v>
@@ -70035,7 +70032,7 @@
         <v>0</v>
       </c>
       <c r="DV178" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="DW178" t="n">
         <v>0</v>
@@ -70070,10 +70067,10 @@
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -70115,10 +70112,10 @@
         <v>0</v>
       </c>
       <c r="X179" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="Z179" t="n">
         <v>0</v>
@@ -70142,10 +70139,10 @@
         <v>0</v>
       </c>
       <c r="AG179" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AH179" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI179" t="n">
         <v>0</v>
@@ -70172,10 +70169,10 @@
         <v>0</v>
       </c>
       <c r="AQ179" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="AR179" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AS179" t="n">
         <v>0</v>
@@ -70205,7 +70202,7 @@
         <v>0</v>
       </c>
       <c r="BB179" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BC179" t="n">
         <v>0</v>
@@ -70229,10 +70226,10 @@
         <v>0</v>
       </c>
       <c r="BJ179" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BK179" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="BL179" t="n">
         <v>0</v>
@@ -70271,7 +70268,7 @@
         <v>0</v>
       </c>
       <c r="BX179" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BY179" t="n">
         <v>0</v>
@@ -70304,13 +70301,13 @@
         <v>0</v>
       </c>
       <c r="CI179" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="CJ179" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CK179" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CL179" t="n">
         <v>0</v>
@@ -70322,7 +70319,7 @@
         <v>0</v>
       </c>
       <c r="CO179" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CP179" t="n">
         <v>0</v>
@@ -70343,7 +70340,7 @@
         <v>0</v>
       </c>
       <c r="CV179" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="CW179" t="n">
         <v>0</v>
@@ -70364,7 +70361,7 @@
         <v>0</v>
       </c>
       <c r="DC179" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DD179" t="n">
         <v>0</v>
@@ -70388,10 +70385,10 @@
         <v>0</v>
       </c>
       <c r="DK179" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DL179" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="DM179" t="n">
         <v>0</v>
@@ -70421,7 +70418,7 @@
         <v>0</v>
       </c>
       <c r="DV179" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="DW179" t="n">
         <v>0</v>
@@ -70438,124 +70435,124 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I180" t="n">
+        <v>2</v>
+      </c>
+      <c r="J180" t="n">
+        <v>524</v>
+      </c>
+      <c r="K180" t="n">
+        <v>200</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>955</v>
+      </c>
+      <c r="O180" t="n">
+        <v>1459</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2173</v>
+      </c>
+      <c r="S180" t="n">
+        <v>330</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0</v>
+      </c>
+      <c r="V180" t="n">
+        <v>21</v>
+      </c>
+      <c r="W180" t="n">
+        <v>159</v>
+      </c>
+      <c r="X180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>88</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>56</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>111</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>196</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>362</v>
+      </c>
+      <c r="AK180" t="n">
         <v>3</v>
       </c>
-      <c r="J180" t="n">
-        <v>10</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" t="n">
-        <v>0</v>
-      </c>
-      <c r="W180" t="n">
-        <v>0</v>
-      </c>
-      <c r="X180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK180" t="n">
-        <v>0</v>
-      </c>
       <c r="AL180" t="n">
         <v>0</v>
       </c>
       <c r="AM180" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AN180" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AO180" t="n">
         <v>0</v>
       </c>
       <c r="AP180" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ180" t="n">
         <v>0</v>
@@ -70564,10 +70561,10 @@
         <v>0</v>
       </c>
       <c r="AS180" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="AU180" t="n">
         <v>0</v>
@@ -70636,7 +70633,7 @@
         <v>0</v>
       </c>
       <c r="BQ180" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BR180" t="n">
         <v>0</v>
@@ -70738,7 +70735,7 @@
         <v>0</v>
       </c>
       <c r="CY180" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="CZ180" t="n">
         <v>0</v>
@@ -70762,7 +70759,7 @@
         <v>0</v>
       </c>
       <c r="DG180" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="DH180" t="n">
         <v>0</v>
@@ -70795,13 +70792,13 @@
         <v>0</v>
       </c>
       <c r="DR180" t="n">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="DS180" t="n">
         <v>0</v>
       </c>
       <c r="DT180" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="DU180" t="n">
         <v>0</v>
@@ -70810,10 +70807,10 @@
         <v>0</v>
       </c>
       <c r="DW180" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="DX180" t="n">
-        <v>0</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="181">
@@ -70824,194 +70821,194 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>1165</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>1029</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>1018</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>228</v>
+      </c>
+      <c r="K181" t="n">
+        <v>194</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>284</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>176</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM181" t="n">
         <v>2</v>
       </c>
-      <c r="J181" t="n">
-        <v>524</v>
-      </c>
-      <c r="K181" t="n">
-        <v>200</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>955</v>
-      </c>
-      <c r="O181" t="n">
-        <v>1459</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>2173</v>
-      </c>
-      <c r="S181" t="n">
-        <v>330</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" t="n">
-        <v>21</v>
-      </c>
-      <c r="W181" t="n">
-        <v>159</v>
-      </c>
-      <c r="X181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>88</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>56</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>111</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>196</v>
-      </c>
-      <c r="AJ181" t="n">
-        <v>362</v>
-      </c>
-      <c r="AK181" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM181" t="n">
-        <v>168</v>
-      </c>
-      <c r="AN181" t="n">
-        <v>165</v>
-      </c>
-      <c r="AO181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP181" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS181" t="n">
-        <v>201</v>
-      </c>
-      <c r="AT181" t="n">
-        <v>161</v>
-      </c>
-      <c r="AU181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL181" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM181" t="n">
-        <v>0</v>
-      </c>
       <c r="BN181" t="n">
         <v>0</v>
       </c>
@@ -71022,7 +71019,7 @@
         <v>0</v>
       </c>
       <c r="BQ181" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BR181" t="n">
         <v>0</v>
@@ -71124,7 +71121,7 @@
         <v>0</v>
       </c>
       <c r="CY181" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="CZ181" t="n">
         <v>0</v>
@@ -71148,7 +71145,7 @@
         <v>0</v>
       </c>
       <c r="DG181" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="DH181" t="n">
         <v>0</v>
@@ -71181,13 +71178,13 @@
         <v>0</v>
       </c>
       <c r="DR181" t="n">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="DS181" t="n">
         <v>0</v>
       </c>
       <c r="DT181" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="DU181" t="n">
         <v>0</v>
@@ -71196,10 +71193,10 @@
         <v>0</v>
       </c>
       <c r="DW181" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="DX181" t="n">
-        <v>1059</v>
+        <v>140</v>
       </c>
     </row>
     <row r="182">
@@ -71231,10 +71228,10 @@
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>228</v>
+        <v>2</v>
       </c>
       <c r="K182" t="n">
-        <v>194</v>
+        <v>3</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -71255,10 +71252,10 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S182" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T182" t="n">
         <v>0</v>
@@ -71279,7 +71276,7 @@
         <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -71306,10 +71303,10 @@
         <v>0</v>
       </c>
       <c r="AI182" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ182" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="AK182" t="n">
         <v>0</v>
@@ -71336,10 +71333,10 @@
         <v>0</v>
       </c>
       <c r="AS182" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="AT182" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="n">
         <v>0</v>
@@ -71369,7 +71366,7 @@
         <v>0</v>
       </c>
       <c r="BD182" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BE182" t="n">
         <v>0</v>
@@ -71396,7 +71393,7 @@
         <v>0</v>
       </c>
       <c r="BM182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BN182" t="n">
         <v>0</v>
@@ -71585,7 +71582,7 @@
         <v>0</v>
       </c>
       <c r="DX182" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -71617,265 +71614,265 @@
         <v>0</v>
       </c>
       <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>20</v>
+      </c>
+      <c r="V183" t="n">
+        <v>0</v>
+      </c>
+      <c r="W183" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO183" t="n">
         <v>1</v>
       </c>
-      <c r="K183" t="n">
+      <c r="BP183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ183" t="n">
+        <v>24</v>
+      </c>
+      <c r="BR183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB183" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC183" t="n">
+        <v>11</v>
+      </c>
+      <c r="CD183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE183" t="n">
+        <v>63</v>
+      </c>
+      <c r="CF183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM183" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN183" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO183" t="n">
         <v>3</v>
       </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>1</v>
-      </c>
-      <c r="S183" t="n">
-        <v>18</v>
-      </c>
-      <c r="T183" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" t="n">
-        <v>0</v>
-      </c>
-      <c r="W183" t="n">
-        <v>0</v>
-      </c>
-      <c r="X183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY183" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM183" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY183" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN183" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO183" t="n">
-        <v>0</v>
-      </c>
       <c r="CP183" t="n">
         <v>0</v>
       </c>
       <c r="CQ183" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="CR183" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="CS183" t="n">
         <v>0</v>
@@ -71905,7 +71902,7 @@
         <v>0</v>
       </c>
       <c r="DB183" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="DC183" t="n">
         <v>0</v>
@@ -71914,13 +71911,13 @@
         <v>0</v>
       </c>
       <c r="DE183" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="DF183" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="DG183" t="n">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="DH183" t="n">
         <v>0</v>
@@ -72036,7 +72033,7 @@
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V184" t="n">
         <v>0</v>
@@ -72054,10 +72051,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -72084,10 +72081,10 @@
         <v>0</v>
       </c>
       <c r="AK184" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AL184" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AM184" t="n">
         <v>0</v>
@@ -72114,10 +72111,10 @@
         <v>0</v>
       </c>
       <c r="AU184" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AV184" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="AW184" t="n">
         <v>0</v>
@@ -72171,22 +72168,22 @@
         <v>0</v>
       </c>
       <c r="BN184" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BO184" t="n">
-        <v>1</v>
+        <v>189</v>
       </c>
       <c r="BP184" t="n">
         <v>0</v>
       </c>
       <c r="BQ184" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BR184" t="n">
         <v>0</v>
       </c>
       <c r="BS184" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT184" t="n">
         <v>0</v>
@@ -72213,16 +72210,16 @@
         <v>0</v>
       </c>
       <c r="CB184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC184" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CD184" t="n">
         <v>0</v>
       </c>
       <c r="CE184" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="CF184" t="n">
         <v>0</v>
@@ -72249,19 +72246,19 @@
         <v>0</v>
       </c>
       <c r="CN184" t="n">
-        <v>2</v>
+        <v>196</v>
       </c>
       <c r="CO184" t="n">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="CP184" t="n">
         <v>0</v>
       </c>
       <c r="CQ184" t="n">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="CR184" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="CS184" t="n">
         <v>0</v>
@@ -72291,7 +72288,7 @@
         <v>0</v>
       </c>
       <c r="DB184" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="DC184" t="n">
         <v>0</v>
@@ -72300,13 +72297,13 @@
         <v>0</v>
       </c>
       <c r="DE184" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="DF184" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="DG184" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="DH184" t="n">
         <v>0</v>
@@ -72377,10 +72374,10 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -72440,10 +72437,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -72500,10 +72497,10 @@
         <v>0</v>
       </c>
       <c r="AU185" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AV185" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AW185" t="n">
         <v>0</v>
@@ -72557,10 +72554,10 @@
         <v>0</v>
       </c>
       <c r="BN185" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO185" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="BP185" t="n">
         <v>0</v>
@@ -72635,10 +72632,10 @@
         <v>0</v>
       </c>
       <c r="CN185" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="CO185" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="CP185" t="n">
         <v>0</v>
@@ -72763,10 +72760,10 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -72775,10 +72772,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K186" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -73161,16 +73158,16 @@
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="N187" t="n">
         <v>0</v>
@@ -73212,10 +73209,10 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -73242,10 +73239,10 @@
         <v>0</v>
       </c>
       <c r="AK187" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AL187" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM187" t="n">
         <v>0</v>
@@ -73272,7 +73269,7 @@
         <v>0</v>
       </c>
       <c r="AU187" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AV187" t="n">
         <v>0</v>
@@ -73302,10 +73299,10 @@
         <v>0</v>
       </c>
       <c r="BE187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF187" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG187" t="n">
         <v>0</v>
@@ -73329,10 +73326,10 @@
         <v>0</v>
       </c>
       <c r="BN187" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BO187" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BP187" t="n">
         <v>0</v>
@@ -73371,13 +73368,13 @@
         <v>0</v>
       </c>
       <c r="CB187" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="CC187" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CD187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CE187" t="n">
         <v>0</v>
@@ -73407,10 +73404,10 @@
         <v>0</v>
       </c>
       <c r="CN187" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CO187" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CP187" t="n">
         <v>0</v>
@@ -73452,7 +73449,7 @@
         <v>0</v>
       </c>
       <c r="DC187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD187" t="n">
         <v>0</v>
@@ -73494,7 +73491,7 @@
         <v>0</v>
       </c>
       <c r="DQ187" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="DR187" t="n">
         <v>0</v>
@@ -73553,10 +73550,10 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
         <v>0</v>
@@ -73598,10 +73595,10 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -73628,10 +73625,10 @@
         <v>0</v>
       </c>
       <c r="AK188" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="AL188" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AM188" t="n">
         <v>0</v>
@@ -73658,7 +73655,7 @@
         <v>0</v>
       </c>
       <c r="AU188" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="AV188" t="n">
         <v>0</v>
@@ -73688,10 +73685,10 @@
         <v>0</v>
       </c>
       <c r="BE188" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF188" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BG188" t="n">
         <v>0</v>
@@ -73715,10 +73712,10 @@
         <v>0</v>
       </c>
       <c r="BN188" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BO188" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BP188" t="n">
         <v>0</v>
@@ -73757,13 +73754,13 @@
         <v>0</v>
       </c>
       <c r="CB188" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="CC188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CD188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CE188" t="n">
         <v>0</v>
@@ -73793,10 +73790,10 @@
         <v>0</v>
       </c>
       <c r="CN188" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CO188" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CP188" t="n">
         <v>0</v>
@@ -73838,7 +73835,7 @@
         <v>0</v>
       </c>
       <c r="DC188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD188" t="n">
         <v>0</v>
@@ -73880,7 +73877,7 @@
         <v>0</v>
       </c>
       <c r="DQ188" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="DR188" t="n">
         <v>0</v>
@@ -73921,10 +73918,10 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -74014,44 +74011,44 @@
         <v>0</v>
       </c>
       <c r="AK189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW189" t="n">
         <v>2</v>
       </c>
-      <c r="AL189" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV189" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW189" t="n">
-        <v>0</v>
-      </c>
       <c r="AX189" t="n">
         <v>0</v>
       </c>
@@ -74110,13 +74107,13 @@
         <v>0</v>
       </c>
       <c r="BQ189" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="BR189" t="n">
         <v>0</v>
       </c>
       <c r="BS189" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="BT189" t="n">
         <v>0</v>
@@ -74146,7 +74143,7 @@
         <v>0</v>
       </c>
       <c r="CC189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CD189" t="n">
         <v>0</v>
@@ -74155,7 +74152,7 @@
         <v>0</v>
       </c>
       <c r="CF189" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CG189" t="n">
         <v>0</v>
@@ -74233,7 +74230,7 @@
         <v>0</v>
       </c>
       <c r="DF189" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="DG189" t="n">
         <v>0</v>
@@ -74301,16 +74298,16 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F190" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -74409,7 +74406,7 @@
         <v>0</v>
       </c>
       <c r="AN190" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AO190" t="n">
         <v>0</v>
@@ -74436,7 +74433,7 @@
         <v>0</v>
       </c>
       <c r="AW190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX190" t="n">
         <v>0</v>
@@ -74496,13 +74493,13 @@
         <v>0</v>
       </c>
       <c r="BQ190" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="BR190" t="n">
         <v>0</v>
       </c>
       <c r="BS190" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="BT190" t="n">
         <v>0</v>
@@ -74541,7 +74538,7 @@
         <v>0</v>
       </c>
       <c r="CF190" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CG190" t="n">
         <v>0</v>
@@ -74619,7 +74616,7 @@
         <v>0</v>
       </c>
       <c r="DF190" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="DG190" t="n">
         <v>0</v>
@@ -74681,23 +74678,23 @@
         <v>317</v>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>5</v>
+      </c>
+      <c r="G191" t="n">
         <v>7</v>
       </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0</v>
-      </c>
       <c r="H191" t="n">
         <v>0</v>
       </c>
@@ -74717,7 +74714,7 @@
         <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -74762,7 +74759,7 @@
         <v>0</v>
       </c>
       <c r="AC191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD191" t="n">
         <v>0</v>
@@ -74786,16 +74783,16 @@
         <v>0</v>
       </c>
       <c r="AK191" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AL191" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AM191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN191" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO191" t="n">
         <v>0</v>
@@ -74819,7 +74816,7 @@
         <v>0</v>
       </c>
       <c r="AV191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW191" t="n">
         <v>0</v>
@@ -74849,7 +74846,7 @@
         <v>0</v>
       </c>
       <c r="BF191" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BG191" t="n">
         <v>0</v>
@@ -74876,13 +74873,13 @@
         <v>0</v>
       </c>
       <c r="BO191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP191" t="n">
         <v>0</v>
       </c>
       <c r="BQ191" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BR191" t="n">
         <v>0</v>
@@ -74915,19 +74912,19 @@
         <v>0</v>
       </c>
       <c r="CB191" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CC191" t="n">
         <v>0</v>
       </c>
       <c r="CD191" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CE191" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="CF191" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="CG191" t="n">
         <v>0</v>
@@ -74951,10 +74948,10 @@
         <v>0</v>
       </c>
       <c r="CN191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO191" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CP191" t="n">
         <v>0</v>
@@ -74963,7 +74960,7 @@
         <v>0</v>
       </c>
       <c r="CR191" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="CS191" t="n">
         <v>0</v>
@@ -75005,10 +75002,10 @@
         <v>0</v>
       </c>
       <c r="DF191" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="DG191" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="DH191" t="n">
         <v>0</v>
@@ -75067,22 +75064,22 @@
         <v>318</v>
       </c>
       <c r="B192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F192" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -75103,7 +75100,7 @@
         <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -75148,7 +75145,7 @@
         <v>0</v>
       </c>
       <c r="AC192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD192" t="n">
         <v>0</v>
@@ -75172,16 +75169,16 @@
         <v>0</v>
       </c>
       <c r="AK192" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL192" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AM192" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN192" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO192" t="n">
         <v>0</v>
@@ -75205,7 +75202,7 @@
         <v>0</v>
       </c>
       <c r="AV192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW192" t="n">
         <v>0</v>
@@ -75235,7 +75232,7 @@
         <v>0</v>
       </c>
       <c r="BF192" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BG192" t="n">
         <v>0</v>
@@ -75262,13 +75259,13 @@
         <v>0</v>
       </c>
       <c r="BO192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP192" t="n">
         <v>0</v>
       </c>
       <c r="BQ192" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BR192" t="n">
         <v>0</v>
@@ -75301,19 +75298,19 @@
         <v>0</v>
       </c>
       <c r="CB192" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CC192" t="n">
         <v>0</v>
       </c>
       <c r="CD192" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CE192" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="CF192" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="CG192" t="n">
         <v>0</v>
@@ -75337,10 +75334,10 @@
         <v>0</v>
       </c>
       <c r="CN192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO192" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CP192" t="n">
         <v>0</v>
@@ -75349,7 +75346,7 @@
         <v>0</v>
       </c>
       <c r="CR192" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="CS192" t="n">
         <v>0</v>
@@ -75391,10 +75388,10 @@
         <v>0</v>
       </c>
       <c r="DF192" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="DG192" t="n">
-        <v>1056</v>
+        <v>0</v>
       </c>
       <c r="DH192" t="n">
         <v>0</v>
@@ -75459,10 +75456,10 @@
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -75558,10 +75555,10 @@
         <v>0</v>
       </c>
       <c r="AK193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL193" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM193" t="n">
         <v>0</v>
@@ -75839,10 +75836,10 @@
         <v>320</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -75869,13 +75866,13 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -75893,10 +75890,10 @@
         <v>0</v>
       </c>
       <c r="T194" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U194" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="V194" t="n">
         <v>0</v>
@@ -75914,10 +75911,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -75944,10 +75941,10 @@
         <v>0</v>
       </c>
       <c r="AK194" t="n">
-        <v>1</v>
+        <v>554</v>
       </c>
       <c r="AL194" t="n">
-        <v>6</v>
+        <v>683</v>
       </c>
       <c r="AM194" t="n">
         <v>0</v>
@@ -75974,10 +75971,10 @@
         <v>0</v>
       </c>
       <c r="AU194" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="AV194" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="AW194" t="n">
         <v>0</v>
@@ -76004,10 +76001,10 @@
         <v>0</v>
       </c>
       <c r="BE194" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="BF194" t="n">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="BG194" t="n">
         <v>0</v>
@@ -76031,22 +76028,22 @@
         <v>0</v>
       </c>
       <c r="BN194" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="BO194" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BP194" t="n">
         <v>0</v>
       </c>
       <c r="BQ194" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BR194" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="BS194" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BT194" t="n">
         <v>0</v>
@@ -76073,19 +76070,19 @@
         <v>0</v>
       </c>
       <c r="CB194" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="CC194" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="CD194" t="n">
-        <v>0</v>
+        <v>2386</v>
       </c>
       <c r="CE194" t="n">
         <v>0</v>
       </c>
       <c r="CF194" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="CG194" t="n">
         <v>0</v>
@@ -76109,22 +76106,22 @@
         <v>0</v>
       </c>
       <c r="CN194" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="CO194" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="CP194" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="CQ194" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="CR194" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="CS194" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="CT194" t="n">
         <v>0</v>
@@ -76151,22 +76148,22 @@
         <v>0</v>
       </c>
       <c r="DB194" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="DC194" t="n">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="DD194" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="DE194" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="DF194" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="DG194" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="DH194" t="n">
         <v>0</v>
@@ -76196,10 +76193,10 @@
         <v>0</v>
       </c>
       <c r="DQ194" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="DR194" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="DS194" t="n">
         <v>0</v>
@@ -76208,7 +76205,7 @@
         <v>0</v>
       </c>
       <c r="DU194" t="n">
-        <v>0</v>
+        <v>2277</v>
       </c>
       <c r="DV194" t="n">
         <v>0</v>
@@ -76225,22 +76222,22 @@
         <v>321</v>
       </c>
       <c r="B195" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -76255,13 +76252,13 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>1609</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -76279,10 +76276,10 @@
         <v>0</v>
       </c>
       <c r="T195" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U195" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="V195" t="n">
         <v>0</v>
@@ -76300,10 +76297,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>723</v>
+        <v>0</v>
       </c>
       <c r="AB195" t="n">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -76330,10 +76327,10 @@
         <v>0</v>
       </c>
       <c r="AK195" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="AL195" t="n">
-        <v>683</v>
+        <v>0</v>
       </c>
       <c r="AM195" t="n">
         <v>0</v>
@@ -76360,10 +76357,10 @@
         <v>0</v>
       </c>
       <c r="AU195" t="n">
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="AV195" t="n">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="AW195" t="n">
         <v>0</v>
@@ -76390,10 +76387,10 @@
         <v>0</v>
       </c>
       <c r="BE195" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="BF195" t="n">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="BG195" t="n">
         <v>0</v>
@@ -76417,22 +76414,22 @@
         <v>0</v>
       </c>
       <c r="BN195" t="n">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="BO195" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BP195" t="n">
         <v>0</v>
       </c>
       <c r="BQ195" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BR195" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="BS195" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BT195" t="n">
         <v>0</v>
@@ -76459,19 +76456,19 @@
         <v>0</v>
       </c>
       <c r="CB195" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="CC195" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="CD195" t="n">
-        <v>2386</v>
+        <v>0</v>
       </c>
       <c r="CE195" t="n">
         <v>0</v>
       </c>
       <c r="CF195" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="CG195" t="n">
         <v>0</v>
@@ -76495,22 +76492,22 @@
         <v>0</v>
       </c>
       <c r="CN195" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="CO195" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="CP195" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="CQ195" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="CR195" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="CS195" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="CT195" t="n">
         <v>0</v>
@@ -76537,22 +76534,22 @@
         <v>0</v>
       </c>
       <c r="DB195" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="DC195" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="DD195" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="DE195" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="DF195" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="DG195" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="DH195" t="n">
         <v>0</v>
@@ -76582,10 +76579,10 @@
         <v>0</v>
       </c>
       <c r="DQ195" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="DR195" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="DS195" t="n">
         <v>0</v>
@@ -76594,7 +76591,7 @@
         <v>0</v>
       </c>
       <c r="DU195" t="n">
-        <v>2277</v>
+        <v>0</v>
       </c>
       <c r="DV195" t="n">
         <v>0</v>
@@ -76617,77 +76614,77 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" t="n">
+        <v>0</v>
+      </c>
+      <c r="W196" t="n">
+        <v>0</v>
+      </c>
+      <c r="X196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA196" t="n">
         <v>1</v>
       </c>
-      <c r="H196" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0</v>
-      </c>
-      <c r="M196" t="n">
-        <v>0</v>
-      </c>
-      <c r="N196" t="n">
-        <v>0</v>
-      </c>
-      <c r="O196" t="n">
-        <v>0</v>
-      </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" t="n">
-        <v>0</v>
-      </c>
-      <c r="T196" t="n">
-        <v>0</v>
-      </c>
-      <c r="U196" t="n">
-        <v>0</v>
-      </c>
-      <c r="V196" t="n">
-        <v>0</v>
-      </c>
-      <c r="W196" t="n">
-        <v>0</v>
-      </c>
-      <c r="X196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z196" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA196" t="n">
-        <v>0</v>
-      </c>
       <c r="AB196" t="n">
         <v>0</v>
       </c>
@@ -76716,10 +76713,10 @@
         <v>0</v>
       </c>
       <c r="AK196" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL196" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM196" t="n">
         <v>0</v>
@@ -76776,10 +76773,10 @@
         <v>0</v>
       </c>
       <c r="BE196" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="BF196" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="BG196" t="n">
         <v>0</v>
@@ -76803,7 +76800,7 @@
         <v>0</v>
       </c>
       <c r="BN196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BO196" t="n">
         <v>0</v>
@@ -76845,10 +76842,10 @@
         <v>0</v>
       </c>
       <c r="CB196" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CC196" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="CD196" t="n">
         <v>0</v>
@@ -76905,7 +76902,7 @@
         <v>0</v>
       </c>
       <c r="CV196" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="CW196" t="n">
         <v>0</v>
@@ -76923,13 +76920,13 @@
         <v>0</v>
       </c>
       <c r="DB196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DC196" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="DD196" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="DE196" t="n">
         <v>0</v>
@@ -77000,7 +76997,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D197" t="n">
         <v>0</v>
@@ -77030,7 +77027,7 @@
         <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N197" t="n">
         <v>0</v>
@@ -77072,100 +77069,100 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>39</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>38</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE197" t="n">
         <v>1</v>
       </c>
-      <c r="AB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK197" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL197" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE197" t="n">
-        <v>382</v>
-      </c>
       <c r="BF197" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="BG197" t="n">
         <v>0</v>
@@ -77189,97 +77186,97 @@
         <v>0</v>
       </c>
       <c r="BN197" t="n">
+        <v>257</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>49</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR197" t="n">
+        <v>44</v>
+      </c>
+      <c r="BS197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB197" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM197" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN197" t="n">
+        <v>71</v>
+      </c>
+      <c r="CO197" t="n">
         <v>3</v>
       </c>
-      <c r="BO197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY197" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB197" t="n">
-        <v>24</v>
-      </c>
-      <c r="CC197" t="n">
-        <v>407</v>
-      </c>
-      <c r="CD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN197" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO197" t="n">
-        <v>0</v>
-      </c>
       <c r="CP197" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="CQ197" t="n">
         <v>0</v>
       </c>
       <c r="CR197" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="CS197" t="n">
         <v>0</v>
@@ -77291,7 +77288,7 @@
         <v>0</v>
       </c>
       <c r="CV197" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="CW197" t="n">
         <v>0</v>
@@ -77309,13 +77306,13 @@
         <v>0</v>
       </c>
       <c r="DB197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DC197" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="DD197" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="DE197" t="n">
         <v>0</v>
@@ -77324,7 +77321,7 @@
         <v>0</v>
       </c>
       <c r="DG197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH197" t="n">
         <v>0</v>
@@ -77386,13 +77383,13 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -77416,7 +77413,7 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
         <v>0</v>
@@ -77458,10 +77455,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -77518,10 +77515,10 @@
         <v>0</v>
       </c>
       <c r="AU198" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="AV198" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AW198" t="n">
         <v>0</v>
@@ -77548,10 +77545,10 @@
         <v>0</v>
       </c>
       <c r="BE198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG198" t="n">
         <v>0</v>
@@ -77575,10 +77572,10 @@
         <v>0</v>
       </c>
       <c r="BN198" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="BO198" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="BP198" t="n">
         <v>0</v>
@@ -77587,7 +77584,7 @@
         <v>0</v>
       </c>
       <c r="BR198" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BS198" t="n">
         <v>0</v>
@@ -77617,7 +77614,7 @@
         <v>0</v>
       </c>
       <c r="CB198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CC198" t="n">
         <v>0</v>
@@ -77653,19 +77650,19 @@
         <v>0</v>
       </c>
       <c r="CN198" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="CO198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CP198" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="CQ198" t="n">
         <v>0</v>
       </c>
       <c r="CR198" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="CS198" t="n">
         <v>0</v>
@@ -77710,7 +77707,7 @@
         <v>0</v>
       </c>
       <c r="DG198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH198" t="n">
         <v>0</v>
@@ -77778,107 +77775,107 @@
         <v>0</v>
       </c>
       <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" t="n">
+        <v>0</v>
+      </c>
+      <c r="W199" t="n">
+        <v>0</v>
+      </c>
+      <c r="X199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL199" t="n">
         <v>2</v>
       </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>0</v>
-      </c>
-      <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" t="n">
-        <v>0</v>
-      </c>
-      <c r="U199" t="n">
-        <v>0</v>
-      </c>
-      <c r="V199" t="n">
-        <v>0</v>
-      </c>
-      <c r="W199" t="n">
-        <v>0</v>
-      </c>
-      <c r="X199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>0</v>
-      </c>
       <c r="AM199" t="n">
         <v>0</v>
       </c>
@@ -77904,10 +77901,10 @@
         <v>0</v>
       </c>
       <c r="AU199" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AV199" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW199" t="n">
         <v>0</v>
@@ -77937,7 +77934,7 @@
         <v>0</v>
       </c>
       <c r="BF199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG199" t="n">
         <v>0</v>
@@ -77961,10 +77958,10 @@
         <v>0</v>
       </c>
       <c r="BN199" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="BO199" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BP199" t="n">
         <v>0</v>
@@ -78009,7 +78006,7 @@
         <v>0</v>
       </c>
       <c r="CD199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE199" t="n">
         <v>0</v>
@@ -78039,19 +78036,19 @@
         <v>0</v>
       </c>
       <c r="CN199" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="CO199" t="n">
         <v>0</v>
       </c>
       <c r="CP199" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="CQ199" t="n">
         <v>0</v>
       </c>
       <c r="CR199" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CS199" t="n">
         <v>0</v>
@@ -78090,13 +78087,13 @@
         <v>0</v>
       </c>
       <c r="DE199" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="DF199" t="n">
         <v>0</v>
       </c>
       <c r="DG199" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DH199" t="n">
         <v>0</v>
@@ -78179,10 +78176,10 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K200" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -78230,10 +78227,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -78260,10 +78257,10 @@
         <v>0</v>
       </c>
       <c r="AK200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM200" t="n">
         <v>0</v>
@@ -78290,10 +78287,10 @@
         <v>0</v>
       </c>
       <c r="AU200" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AV200" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW200" t="n">
         <v>0</v>
@@ -78323,7 +78320,7 @@
         <v>0</v>
       </c>
       <c r="BF200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG200" t="n">
         <v>0</v>
@@ -78347,10 +78344,10 @@
         <v>0</v>
       </c>
       <c r="BN200" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="BO200" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BP200" t="n">
         <v>0</v>
@@ -78395,7 +78392,7 @@
         <v>0</v>
       </c>
       <c r="CD200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CE200" t="n">
         <v>0</v>
@@ -78425,19 +78422,19 @@
         <v>0</v>
       </c>
       <c r="CN200" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="CO200" t="n">
         <v>0</v>
       </c>
       <c r="CP200" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CQ200" t="n">
         <v>0</v>
       </c>
       <c r="CR200" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CS200" t="n">
         <v>0</v>
@@ -78476,13 +78473,13 @@
         <v>0</v>
       </c>
       <c r="DE200" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="DF200" t="n">
         <v>0</v>
       </c>
       <c r="DG200" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="DH200" t="n">
         <v>0</v>
@@ -78541,19 +78538,19 @@
         <v>327</v>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -78562,94 +78559,94 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J201" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K201" t="n">
+        <v>27</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>2</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>18</v>
+      </c>
+      <c r="S201" t="n">
+        <v>7</v>
+      </c>
+      <c r="T201" t="n">
+        <v>68</v>
+      </c>
+      <c r="U201" t="n">
+        <v>14</v>
+      </c>
+      <c r="V201" t="n">
+        <v>0</v>
+      </c>
+      <c r="W201" t="n">
+        <v>0</v>
+      </c>
+      <c r="X201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ201" t="n">
         <v>5</v>
       </c>
-      <c r="L201" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="n">
-        <v>0</v>
-      </c>
-      <c r="T201" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" t="n">
-        <v>0</v>
-      </c>
-      <c r="V201" t="n">
-        <v>0</v>
-      </c>
-      <c r="W201" t="n">
-        <v>0</v>
-      </c>
-      <c r="X201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ201" t="n">
-        <v>0</v>
-      </c>
       <c r="AK201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL201" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM201" t="n">
         <v>0</v>
@@ -78670,7 +78667,7 @@
         <v>0</v>
       </c>
       <c r="AS201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT201" t="n">
         <v>0</v>
@@ -78709,7 +78706,7 @@
         <v>0</v>
       </c>
       <c r="BF201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG201" t="n">
         <v>0</v>
@@ -78898,7 +78895,7 @@
         <v>0</v>
       </c>
       <c r="DQ201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DR201" t="n">
         <v>0</v>
@@ -78907,7 +78904,7 @@
         <v>0</v>
       </c>
       <c r="DT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU201" t="n">
         <v>0</v>
@@ -78927,19 +78924,19 @@
         <v>328</v>
       </c>
       <c r="B202" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -78948,19 +78945,19 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K202" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
         <v>0</v>
@@ -78975,16 +78972,16 @@
         <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="U202" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V202" t="n">
         <v>0</v>
@@ -79029,13 +79026,13 @@
         <v>0</v>
       </c>
       <c r="AJ202" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL202" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM202" t="n">
         <v>0</v>
@@ -79056,7 +79053,7 @@
         <v>0</v>
       </c>
       <c r="AS202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT202" t="n">
         <v>0</v>
@@ -79095,7 +79092,7 @@
         <v>0</v>
       </c>
       <c r="BF202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG202" t="n">
         <v>0</v>
@@ -79284,7 +79281,7 @@
         <v>0</v>
       </c>
       <c r="DQ202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DR202" t="n">
         <v>0</v>
@@ -79293,7 +79290,7 @@
         <v>0</v>
       </c>
       <c r="DT202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU202" t="n">
         <v>0</v>
@@ -79337,10 +79334,10 @@
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -79442,10 +79439,10 @@
         <v>0</v>
       </c>
       <c r="AS203" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>722</v>
       </c>
       <c r="AU203" t="n">
         <v>0</v>
@@ -79499,10 +79496,10 @@
         <v>0</v>
       </c>
       <c r="BL203" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="BM203" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="BN203" t="n">
         <v>0</v>
@@ -79828,10 +79825,10 @@
         <v>0</v>
       </c>
       <c r="AS204" t="n">
-        <v>619</v>
+        <v>5</v>
       </c>
       <c r="AT204" t="n">
-        <v>722</v>
+        <v>3</v>
       </c>
       <c r="AU204" t="n">
         <v>0</v>
@@ -79885,10 +79882,10 @@
         <v>0</v>
       </c>
       <c r="BL204" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BM204" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="BN204" t="n">
         <v>0</v>
@@ -80077,392 +80074,6 @@
         <v>0</v>
       </c>
       <c r="DX204" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>331</v>
-      </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
-      <c r="C205" t="n">
-        <v>0</v>
-      </c>
-      <c r="D205" t="n">
-        <v>0</v>
-      </c>
-      <c r="E205" t="n">
-        <v>0</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" t="n">
-        <v>0</v>
-      </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" t="n">
-        <v>0</v>
-      </c>
-      <c r="L205" t="n">
-        <v>0</v>
-      </c>
-      <c r="M205" t="n">
-        <v>0</v>
-      </c>
-      <c r="N205" t="n">
-        <v>0</v>
-      </c>
-      <c r="O205" t="n">
-        <v>0</v>
-      </c>
-      <c r="P205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="n">
-        <v>0</v>
-      </c>
-      <c r="T205" t="n">
-        <v>0</v>
-      </c>
-      <c r="U205" t="n">
-        <v>0</v>
-      </c>
-      <c r="V205" t="n">
-        <v>0</v>
-      </c>
-      <c r="W205" t="n">
-        <v>0</v>
-      </c>
-      <c r="X205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS205" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT205" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY205" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY205" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW205" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX205" t="n">
         <v>0</v>
       </c>
     </row>
